--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_UAT_BRD-11_Business_Unit_Walkthrough_Users_v1.1.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_UAT_BRD-11_Business_Unit_Walkthrough_Users_v1.1.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$27</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Users'!$A$4:$J$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Users'!$A$4:$J$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Users'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Walkthrough script'!$A$4:$J$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Walkthrough script'!$A$4:$M$39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Walkthrough script'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Lists'!$1:$1</definedName>
   </definedNames>
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E31"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -715,13 +715,16 @@
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="40" customHeight="1"/>
+    <row r="3"/>
     <row r="4" ht="6" customHeight="1">
       <c r="B4" s="1" t="n"/>
       <c r="C4" s="1" t="n"/>
       <c r="D4" s="1" t="n"/>
       <c r="E4" s="1" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -739,7 +742,7 @@
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>BRD-11 User Access Maintenance - sign-in IDs for the walkthrough</t>
+          <t>BRD-11 User Access Maintenance - persona users for the walkthroughs</t>
         </is>
       </c>
     </row>
@@ -750,6 +753,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
@@ -822,6 +826,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -871,7 +876,7 @@
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -882,13 +887,14 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>The walkthrough of BRD-11 for the Business Unit (FRS Annex O)</t>
+          <t>The walkthroughs of BRD-11 for the Business Unit, step by step as in FRS Annex O</t>
         </is>
       </c>
       <c r="D22" s="12" t="n">
-        <v>33</v>
-      </c>
-    </row>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="B24" s="9" t="inlineStr">
         <is>
@@ -920,13 +926,15 @@
       </c>
       <c r="C27" s="16" t="inlineStr"/>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>Environment: BIBS DEV environment: https://dev.brokerverse.cloud. Passwords: Issued separately by the iorta TechNXT Project Team; no password is written in this workbook.</t>
-        </is>
-      </c>
-    </row>
+          <t>Environment: BIBS DEV environment: https://dev.brokerverse.cloud. Passwords: Issued separately by the iorta TechNXT Project Team; no password is written in this workbook. The steps, personas, screens and users are those of FRS Annex O; the people named are fictitious.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31" ht="26" customHeight="1">
       <c r="B31" s="19" t="inlineStr">
         <is>
@@ -961,7 +969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -984,6 +992,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -1019,7 +1028,7 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Business role of the FRS</t>
+          <t>Persona of FRS Annex O</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr"/>
@@ -1037,7 +1046,7 @@
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>As shown on the screens</t>
+          <t>Fictitious user of FRS Annex O</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr"/>
@@ -1073,7 +1082,7 @@
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>Role held</t>
+          <t>Group profile held</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr"/>
@@ -1100,10 +1109,14 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>What the user does in the walkthrough</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr"/>
+          <t>What the user does in the walkthroughs</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Results of the user's steps</t>
+        </is>
+      </c>
       <c r="D10" s="14" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1114,7 +1127,7 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>Menu path to start</t>
+          <t>Screen of the first step</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr"/>
@@ -1224,7 +1237,7 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>Sign-in ID</t>
+          <t>User</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr"/>
@@ -1238,7 +1251,7 @@
       </c>
       <c r="B19" s="21" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Sign-in ID</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr"/>
@@ -1252,7 +1265,7 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>Expected result</t>
+          <t>Screen</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr"/>
@@ -1266,15 +1279,11 @@
       </c>
       <c r="B21" s="21" t="inlineStr">
         <is>
-          <t>Result</t>
+          <t>What the user does</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr"/>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>Not run, Pass, Fail, Blocked</t>
-        </is>
-      </c>
+      <c r="D21" s="12" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
@@ -1284,7 +1293,7 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>Done by</t>
+          <t>What the user sees</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr"/>
@@ -1298,7 +1307,7 @@
       </c>
       <c r="B23" s="21" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Result expected</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr"/>
@@ -1312,14 +1321,60 @@
       </c>
       <c r="B24" s="22" t="inlineStr">
         <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr"/>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>Not run, Pass, Fail, Blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Walkthrough script</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>Done by</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr"/>
+      <c r="D25" s="12" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>Walkthrough script</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr"/>
+      <c r="D26" s="14" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Walkthrough script</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
           <t>Remarks</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr"/>
-      <c r="D24" s="14" t="inlineStr"/>
+      <c r="C27" s="12" t="inlineStr"/>
+      <c r="D27" s="12" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D24"/>
+  <autoFilter ref="A4:D27"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -1340,11 +1395,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
@@ -1409,12 +1464,12 @@
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>What the user does in the walkthrough</t>
+          <t>What the user does in the walkthroughs</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>Menu path to start</t>
+          <t>Screen of the first step</t>
         </is>
       </c>
       <c r="H4" s="25" t="inlineStr">
@@ -1441,7 +1496,7 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Rhea Access Requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
@@ -1456,17 +1511,17 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>BDO Insurance and Reinsurance Brokers, Inc. / Head Office - Makati / User Access Maintenance</t>
+          <t>BDO Insurance and Reinsurance Brokers, Inc. / Head Office</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Raises user access requests: enrol, modify, deactivate, reactivate, bulk; corrects and cancels them; views own requests</t>
+          <t>Another password chosen; Another requester raises it; Draft request; Form corrected; One of the two profiles removed; Password rules shown; Pending Approval; User ID corrected; Wait for the open request</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>Setup &amp; Administration › User Access › Access Requests</t>
+          <t>New Request and Edit Request (user requests) (SCR-UA-07)</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -1493,7 +1548,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Ulysses Access Approver</t>
+          <t>Ulysses Abad</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -1508,17 +1563,17 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>BDO Insurance and Reinsurance Brokers, Inc. / Head Office - Makati / User Access Maintenance</t>
+          <t>BDO Insurance and Reinsurance Brokers, Inc. / Head Office</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>Reviews and approves, rejects or returns requests assigned to him or her</t>
+          <t>Approved and applied; Change applied; Next approver; Request found; User deactivated</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>Setup &amp; Administration › User Access › Access Requests</t>
+          <t>Access Requests (SCR-UA-06)</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
@@ -1540,47 +1595,47 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>Approver (New Business Approver</t>
+          <t>Second Approver</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Andres Approver</t>
+          <t>Selina Reyes</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>approver</t>
+          <t>secapprover</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Approver (requests, workload)</t>
+          <t>User Access Second Approver</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>BDO Insurance and Reinsurance Brokers, Inc. / Head Office - Makati / New Business</t>
+          <t>BDO Insurance and Reinsurance Brokers, Inc. / Head Office</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Approves the access and group-profile requests assigned to him or her, as the second approver in order</t>
+          <t>Second approval given</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>Setup &amp; Administration › User Access › Access Requests</t>
+          <t>Access Request record (SCR-UA-08)</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>Home › My Approvals; User Access › Access Requests, Group Profile Requests, Bulk Request, User Access Matrix; Help › My Profile</t>
+          <t>Home › My Approvals; User Access › Access Requests; User Access › Group Profile Requests; Help › My Profile (every user)</t>
         </is>
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>WT-B.6, WT-C.6</t>
+          <t>WT-B.3</t>
         </is>
       </c>
       <c r="J7" s="12" t="inlineStr">
@@ -1592,47 +1647,47 @@
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>Second approver</t>
+          <t>Second approver of the group profile</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Selina Second Approver</t>
+          <t>Andres Bautista</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>secapprover</t>
+          <t>approver</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>User Access Second Approver</t>
+          <t>User Access Approver</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>BDO Insurance and Reinsurance Brokers, Inc. / Head Office - Makati / User Access Maintenance</t>
+          <t>BDO Insurance and Reinsurance Brokers, Inc. / Head Office</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Reviews privileged or out-of-hours changes after the first approval</t>
+          <t>For implementation</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>Setup &amp; Administration › User Access › Access Requests</t>
+          <t>Access Request record (SCR-UA-08)</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>Home › My Approvals; User Access › Access Requests; User Access › Group Profile Requests; Help › My Profile (every user)</t>
+          <t>Home › My Approvals; User Access › Access Requests; User Access › Bulk Request; User Access › Group Profile Requests; User Access › User Access Matrix; User Access › User Access Reports; Help › My Profile (every user)</t>
         </is>
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
-          <t>WT-B.3</t>
+          <t>WT-B.6</t>
         </is>
       </c>
       <c r="J8" s="12" t="inlineStr">
@@ -1644,47 +1699,47 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>Business Administrator</t>
+          <t>Another approver</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Bea Business Admin</t>
+          <t>Andres Bautista</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>approver</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Business Administrator</t>
+          <t>User Access Approver</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>BDO Insurance and Reinsurance Brokers, Inc. / Head Office - Makati / Business Administration</t>
+          <t>BDO Insurance and Reinsurance Brokers, Inc. / Head Office</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>Raises group-profile requests; generates the reports; maintains the separation-of-duties rules; uploads bulk requests; supports users</t>
+          <t>Left to the chosen approver</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>Setup &amp; Administration › User Access › Access Requests</t>
+          <t>Access Request record (SCR-UA-08)</t>
         </is>
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>Home › My Approvals; User Access › Access Requests; User Access › Bulk Request; User Access › Group Profile Requests; User Access › User Access Matrix; User Access › Separation of Duties; User Access › User Access Reports; Administration › Audit Trail; Administration › System Parameters; Administration › Scheduled Jobs; Help › My Profile (every user)</t>
+          <t>Home › My Approvals; User Access › Access Requests; User Access › Bulk Request; User Access › Group Profile Requests; User Access › User Access Matrix; User Access › User Access Reports; Help › My Profile (every user)</t>
         </is>
       </c>
       <c r="I9" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4</t>
+          <t>WT-C.6</t>
         </is>
       </c>
       <c r="J9" s="12" t="inlineStr">
@@ -1696,47 +1751,47 @@
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>System Administrator</t>
+          <t>Business Administrator</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>SIT System Administrator</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>badmin</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>System Administrator</t>
+          <t>Business Administrator</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>BDO Insurance and Reinsurance Brokers, Inc. / Head Office - Makati / IT - System Administration</t>
+          <t>BDO Insurance and Reinsurance Brokers, Inc. / Head Office</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>Implements approved group-profile requests; defines the UAM group profiles and their functions; unlocks users and resets passwords; audit logs</t>
+          <t>Pending Approval (first approver)</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>Setup &amp; Administration › Administration › Roles &amp; Permissions</t>
+          <t>New Group Profile Request and Edit Request (SCR-UA-12)</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>Home › My Approvals; User Access › Access Requests; User Access › Bulk Request; User Access › Group Profile Requests; User Access › User Access Matrix; User Access › User Access Reports; Administration › Users; Administration › Identity Synchronisation; Administration › Roles &amp; Permissions; Administration › Second Factor; Administration › Audit Trail; Administration › System Parameters; Administration › Scheduled Jobs; Help › My Profile (every user)</t>
+          <t>Home › My Approvals; User Access › Access Requests; User Access › Bulk Request; User Access › Group Profile Requests; User Access › User Access Matrix; User Access › Separation of Duties; User Access › User Access Reports; Administration › Audit Trail; Administration › System Parameters; Administration › Scheduled Jobs; Help › My Profile (every user)</t>
         </is>
       </c>
       <c r="I10" s="12" t="inlineStr">
         <is>
-          <t>WT-B.7, WT-B.10, WT-C.7, WT-C.9</t>
+          <t>WT-B.4</t>
         </is>
       </c>
       <c r="J10" s="12" t="inlineStr">
@@ -1748,47 +1803,47 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>Information Security Officer</t>
+          <t>System Administrator</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Ingrid Security Officer</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>infosec</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Information Security Officer</t>
+          <t>System Administrator</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>BDO Insurance and Reinsurance Brokers, Inc. / Head Office - Makati / Information Security</t>
+          <t>BDO Insurance and Reinsurance Brokers, Inc. / Head Office</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>Views the access requests, the group-profile requests and the User Access Matrix, and the audit trail; runs the user access reports; authorises the separation-of-duties rules; approves the changes of the security settings</t>
+          <t>Account unlocked; Another System Administrator implements it; Evidence of the revocation; Implemented</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>Setup &amp; Administration › User Access › Access Requests</t>
+          <t>Roles &amp; Permissions (SCR-UA-16)</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>Home › My Approvals; User Access › Access Requests; User Access › Group Profile Requests; User Access › User Access Matrix; User Access › Separation of Duties; User Access › User Access Reports; Administration › Second Factor; Administration › Audit Trail; Administration › System Parameters; Help › My Profile (every user)</t>
+          <t>Home › My Approvals; User Access › Access Requests; User Access › Bulk Request; User Access › Group Profile Requests; User Access › User Access Matrix; User Access › User Access Reports; Administration › Users; Administration › Identity Synchronisation; Administration › Roles &amp; Permissions; Administration › Second Factor; Administration › Audit Trail; Administration › System Parameters; Administration › Scheduled Jobs; Help › My Profile (every user)</t>
         </is>
       </c>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>Not in a walkthrough step</t>
+          <t>WT-B.7, WT-B.10, WT-C.7, WT-C.9</t>
         </is>
       </c>
       <c r="J11" s="12" t="inlineStr">
@@ -1800,64 +1855,64 @@
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>Auditor</t>
+          <t>New user (Marketing Account Officer)</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>Audrey Auditor</t>
+          <t>Isabel Navarro</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>a013000196</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Auditor</t>
+          <t>Marketing Account Officer</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>BDO Insurance and Reinsurance Brokers, Inc. / Head Office - Makati / Internal Audit</t>
+          <t>BDO Insurance and Reinsurance Brokers, Inc. / Head Office</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>Views requests and runs the reports and the audit log</t>
+          <t>Forced change; Menus of the persona; Signed in</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>Reports › Reports › Report Centre</t>
+          <t>Login (SCR-UA-01)</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>Home › My Approvals; User Access › Access Requests; User Access › Group Profile Requests; User Access › User Access Matrix; User Access › User Access Reports; Administration › Audit Trail; Administration › System Parameters; Administration › Scheduled Jobs; Help › My Profile (every user)</t>
+          <t>The menu of the Marketing Account Officer (no User Access entry); Help › My Profile</t>
         </is>
       </c>
       <c r="I12" s="12" t="inlineStr">
         <is>
-          <t>WT-A.8, WT-D.1, WT-D.2, WT-D.3</t>
+          <t>WT-A.5, WT-A.6, WT-A.7</t>
         </is>
       </c>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>Issued separately by the iorta TechNXT Project Team</t>
+          <t>Temporary password shown once at step WT-A.4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>Subject users of the requests (Marketing AO)</t>
+          <t>Business user</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>SIT Enrolled User</t>
+          <t>Maria Santos</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -1872,17 +1927,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>BDO Insurance and Reinsurance Brokers, Inc. / Head Office - Makati / Marketing</t>
+          <t>BDO Insurance and Reinsurance Brokers, Inc. / Head Office</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>Users whose access the requests enrol, change, deactivate or unlock; a013000101 is locked and unlocked in walkthrough C</t>
+          <t>Account locked; Refused</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>Client &amp; Policy › Clients › Clients</t>
+          <t>Login (SCR-UA-01)</t>
         </is>
       </c>
       <c r="H13" s="12" t="inlineStr">
@@ -1892,7 +1947,7 @@
       </c>
       <c r="I13" s="12" t="inlineStr">
         <is>
-          <t>WT-C.8</t>
+          <t>WT-C.8, WT-C.10</t>
         </is>
       </c>
       <c r="J13" s="12" t="inlineStr">
@@ -1904,47 +1959,47 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>Subject users of the requests (Marketing AO)</t>
+          <t>Auditor</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>SIT Leaver</t>
+          <t>Audrey Lim</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>a013000102</t>
+          <t>auditor</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Marketing Account Officer</t>
+          <t>Auditor</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>BDO Insurance and Reinsurance Brokers, Inc. / Head Office - Makati / Marketing</t>
+          <t>BDO Insurance and Reinsurance Brokers, Inc. / Head Office</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>Users whose access the requests enrol, change, deactivate or unlock; a013000101 is locked and unlocked in walkthrough C</t>
+          <t>Access as of a date reviewed; Evidence of the enrolment; Group-profile changes reviewed; Matrix reviewed; Members reviewed; Profile content reviewed</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>Client &amp; Policy › Clients › Clients</t>
+          <t>User access report (report runner) (SCR-UA-17)</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>The menu of the Marketing Account Officer (no User Access entry); Help › My Profile</t>
+          <t>Home › My Approvals; User Access › Access Requests; User Access › Group Profile Requests; User Access › User Access Matrix; User Access › User Access Reports; Administration › Audit Trail; Administration › System Parameters; Administration › Scheduled Jobs; Help › My Profile (every user)</t>
         </is>
       </c>
       <c r="I14" s="12" t="inlineStr">
         <is>
-          <t>Not in a walkthrough step</t>
+          <t>WT-A.8, WT-D.1, WT-D.2, WT-D.3, WT-D.4, WT-D.5</t>
         </is>
       </c>
       <c r="J14" s="12" t="inlineStr">
@@ -1953,116 +2008,12 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Subject users of the requests (Marketing AO)</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>SIT Transferee</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>a013000103</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Marketing Account Officer</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>BDO Insurance and Reinsurance Brokers, Inc. / Head Office - Makati / Marketing</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>Users whose access the requests enrol, change, deactivate or unlock; a013000101 is locked and unlocked in walkthrough C</t>
-        </is>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>Client &amp; Policy › Clients › Clients</t>
-        </is>
-      </c>
-      <c r="H15" s="12" t="inlineStr">
-        <is>
-          <t>The menu of the Marketing Account Officer (no User Access entry); Help › My Profile</t>
-        </is>
-      </c>
-      <c r="I15" s="12" t="inlineStr">
-        <is>
-          <t>Not in a walkthrough step</t>
-        </is>
-      </c>
-      <c r="J15" s="12" t="inlineStr">
-        <is>
-          <t>Issued separately by the iorta TechNXT Project Team</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>Subject users of the requests (Marketing AO)</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>SIT Team Lead</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>a013000104</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>Marketing Account Officer</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>BDO Insurance and Reinsurance Brokers, Inc. / Head Office - Makati / Marketing</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>Users whose access the requests enrol, change, deactivate or unlock; a013000101 is locked and unlocked in walkthrough C</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>Client &amp; Policy › Clients › Clients</t>
-        </is>
-      </c>
-      <c r="H16" s="12" t="inlineStr">
-        <is>
-          <t>The menu of the Marketing Account Officer (no User Access entry); Help › My Profile</t>
-        </is>
-      </c>
-      <c r="I16" s="12" t="inlineStr">
-        <is>
-          <t>Not in a walkthrough step</t>
-        </is>
-      </c>
-      <c r="J16" s="12" t="inlineStr">
-        <is>
-          <t>Issued separately by the iorta TechNXT Project Team</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:J16"/>
+  <autoFilter ref="A4:J14"/>
   <mergeCells count="1">
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:J516">
+  <conditionalFormatting sqref="A5:J514">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -2087,19 +2038,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="56" customWidth="1" min="5" max="5"/>
-    <col width="56" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="56" customWidth="1" min="7" max="7"/>
+    <col width="56" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2112,7 +2066,7 @@
     <row r="2">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>The walkthrough of BRD-11 for the Business Unit (FRS Annex O)</t>
+          <t>The walkthroughs of BRD-11 for the Business Unit, step by step as in FRS Annex O</t>
         </is>
       </c>
     </row>
@@ -2127,6 +2081,9 @@
       <c r="H3" s="24" t="n"/>
       <c r="I3" s="24" t="n"/>
       <c r="J3" s="24" t="n"/>
+      <c r="K3" s="24" t="n"/>
+      <c r="L3" s="24" t="n"/>
+      <c r="M3" s="24" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="25" t="inlineStr">
@@ -2146,35 +2103,50 @@
       </c>
       <c r="D4" s="25" t="inlineStr">
         <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
           <t>Sign-in ID</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>Expected result</t>
+          <t>Screen</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
+          <t>What the user does</t>
+        </is>
+      </c>
+      <c r="H4" s="25" t="inlineStr">
+        <is>
+          <t>What the user sees</t>
+        </is>
+      </c>
+      <c r="I4" s="25" t="inlineStr">
+        <is>
+          <t>Result expected</t>
+        </is>
+      </c>
+      <c r="J4" s="25" t="inlineStr">
+        <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="H4" s="25" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t>Done by</t>
         </is>
       </c>
-      <c r="I4" s="25" t="inlineStr">
+      <c r="L4" s="25" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="J4" s="25" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -2198,27 +2170,42 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
+          <t>Rhea Santiago</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
           <t>requestor</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>Opens User Access › Access Requests › New Request, keeps Enrol new user, enters the user ID a013000196, the full name, e-mail, Windows ID and home branch, ticks Marketing Account Officer, chooses the approver Ulysses Access Approver, writes the justification and clicks Save Draft</t>
-        </is>
-      </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Toast: AR-yyyy-nnnnnn saved as a draft; the request opens as Draft with Approver Chosen on submission</t>
-        </is>
-      </c>
-      <c r="G5" s="26" t="inlineStr">
+          <t>New Request and Edit Request (user requests) (SCR-UA-07)</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>Opens User Access › Access Requests › New Request, keeps Enrol new user, enters the user ID, full name, e-mail, Windows ID and home branch, ticks Marketing Account Officer, chooses the approver Ulysses Abad, writes the justification and clicks Save Draft</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>The request is saved as a draft with its number; the approver is notified only on submission</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>Draft request [Integration scope - UIDM-ISC]</t>
+        </is>
+      </c>
+      <c r="J5" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr"/>
-      <c r="I5" s="12" t="inlineStr"/>
-      <c r="J5" s="12" t="inlineStr"/>
+      <c r="K5" s="12" t="inlineStr"/>
+      <c r="L5" s="12" t="inlineStr"/>
+      <c r="M5" s="12" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -2238,27 +2225,42 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
+          <t>Rhea Santiago</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
           <t>requestor</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Access Request record (SCR-UA-08)</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>Clicks Edit Request, checks the data and clicks Submit</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>Toast: AR-yyyy-nnnnnn submitted; the status is Pending Approval and the History tab lists Saved and Submitted</t>
-        </is>
-      </c>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>The request is submitted: the status is Pending Approval and the History tab lists Saved and Submitted</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>Pending Approval [Integration scope - UIDM-ISC]</t>
+        </is>
+      </c>
+      <c r="J6" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr"/>
-      <c r="I6" s="12" t="inlineStr"/>
-      <c r="J6" s="12" t="inlineStr"/>
+      <c r="K6" s="12" t="inlineStr"/>
+      <c r="L6" s="12" t="inlineStr"/>
+      <c r="M6" s="12" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -2278,27 +2280,42 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
+          <t>Ulysses Abad</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
           <t>uamapprover</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>Opens the notice Access request AR-yyyy-nnnnnn to approve, or User Access › Access Requests</t>
-        </is>
-      </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>The request is on the Assigned to Me tab with its change: Create user a013000196 with group profiles Marketing Account Officer</t>
-        </is>
-      </c>
-      <c r="G7" s="26" t="inlineStr">
+          <t>Access Requests (SCR-UA-06)</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>Opens the notice of the request to approve, or User Access › Access Requests</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>The request is on the Assigned to Me tab with its change: Create user a013000196 with the group profile Marketing Account Officer</t>
+        </is>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>Request found [Integration scope - UIDM-ISC]</t>
+        </is>
+      </c>
+      <c r="J7" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H7" s="12" t="inlineStr"/>
-      <c r="I7" s="12" t="inlineStr"/>
-      <c r="J7" s="12" t="inlineStr"/>
+      <c r="K7" s="12" t="inlineStr"/>
+      <c r="L7" s="12" t="inlineStr"/>
+      <c r="M7" s="12" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -2318,27 +2335,42 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
+          <t>Ulysses Abad</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
           <t>uamapprover</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Access Request record (SCR-UA-08)</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>Opens the request, reads the Details tab (current and requested values), clicks Approve and Apply, adds a comment and confirms</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>User a013000196 was created, with the temporary password shown once to be given through a secure channel; the status is Approved</t>
-        </is>
-      </c>
-      <c r="G8" s="26" t="inlineStr">
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>The user is created; the temporary password is shown once, to be given through a secure channel; the status is Approved</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>Approved and applied [Integration scope - UIDM-ISC]</t>
+        </is>
+      </c>
+      <c r="J8" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr"/>
-      <c r="I8" s="12" t="inlineStr"/>
-      <c r="J8" s="12" t="inlineStr"/>
+      <c r="K8" s="12" t="inlineStr"/>
+      <c r="L8" s="12" t="inlineStr"/>
+      <c r="M8" s="12" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -2353,32 +2385,47 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Subject users of the requests (Marketing AO)</t>
+          <t>New user (Marketing Account Officer)</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
+          <t>Isabel Navarro</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
           <t>a013000196</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>The new user opens BIBS and signs in with a013000196 and the temporary password</t>
-        </is>
-      </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
+          <t>Login (SCR-UA-01)</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>Opens the system and signs in with the user ID and the temporary password</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
           <t>Change Your Password: Your password was set by an administrator. Choose your own password to continue.</t>
         </is>
       </c>
-      <c r="G9" s="26" t="inlineStr">
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>Forced change</t>
+        </is>
+      </c>
+      <c r="J9" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr"/>
-      <c r="I9" s="12" t="inlineStr"/>
-      <c r="J9" s="12" t="inlineStr"/>
+      <c r="K9" s="12" t="inlineStr"/>
+      <c r="L9" s="12" t="inlineStr"/>
+      <c r="M9" s="12" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -2393,32 +2440,47 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Subject users of the requests (Marketing AO)</t>
+          <t>New user (Marketing Account Officer)</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
+          <t>Isabel Navarro</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
           <t>a013000196</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Change Your Password (forced change) (SCR-UA-03)</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>Enters the temporary password as the current password and a personal password twice, and clicks Change Password</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>Toast: Password changed; the home page opens</t>
-        </is>
-      </c>
-      <c r="G10" s="26" t="inlineStr">
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>Password changed; the home page opens</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>Signed in</t>
+        </is>
+      </c>
+      <c r="J10" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr"/>
-      <c r="I10" s="12" t="inlineStr"/>
-      <c r="J10" s="12" t="inlineStr"/>
+      <c r="K10" s="12" t="inlineStr"/>
+      <c r="L10" s="12" t="inlineStr"/>
+      <c r="M10" s="12" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
@@ -2433,32 +2495,47 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Subject users of the requests (Marketing AO)</t>
+          <t>New user (Marketing Account Officer)</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
+          <t>Isabel Navarro</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
           <t>a013000196</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>Opens the sidebar and My Profile</t>
-        </is>
-      </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>The sidebar holds exactly the entries of the Marketing Account Officer (chapter 12); My Profile lists the group profile Marketing Account Officer and its permissions, and the first session</t>
-        </is>
-      </c>
-      <c r="G11" s="26" t="inlineStr">
+          <t>My Profile (SCR-UA-05)</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>Opens the menu and My Profile</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>The menu holds exactly the entries of the Marketing Account Officer; My Profile lists the group profile Marketing Account Officer, its permissions and the first session</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>Menus of the persona</t>
+        </is>
+      </c>
+      <c r="J11" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr"/>
-      <c r="I11" s="12" t="inlineStr"/>
-      <c r="J11" s="12" t="inlineStr"/>
+      <c r="K11" s="12" t="inlineStr"/>
+      <c r="L11" s="12" t="inlineStr"/>
+      <c r="M11" s="12" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -2478,27 +2555,42 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
+          <t>Audrey Lim</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
           <t>auditor</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>User access report (report runner) (SCR-UA-17)</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>Opens User Access Reports › User Access Audit Log for today, ticks Include Log-ins and Log-outs and clicks Run Report</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>Enroll New User a013000196 with the from and to values of the full name, e-mail and profiles, Done By and Approved By the Approver, the request number, and the Log-in of the new user</t>
-        </is>
-      </c>
-      <c r="G12" s="26" t="inlineStr">
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>Enrol New User with the from and to values of the full name, e-mail and profiles, Done By and Approved By, the request number, and the first sign-in of the new user</t>
+        </is>
+      </c>
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>Evidence of the enrolment</t>
+        </is>
+      </c>
+      <c r="J12" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr"/>
-      <c r="I12" s="12" t="inlineStr"/>
-      <c r="J12" s="12" t="inlineStr"/>
+      <c r="K12" s="12" t="inlineStr"/>
+      <c r="L12" s="12" t="inlineStr"/>
+      <c r="M12" s="12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -2518,27 +2610,42 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
+          <t>Rhea Santiago</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
           <t>requestor</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>Opens a New Request of type Modify user for a013000196, ticks Marketing Team Leader / Head (approver) besides the current profile, chooses the approver, writes the justification and clicks Submit</t>
-        </is>
-      </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>The Group Profiles show (current) after Marketing Account Officer; toast AR-yyyy-nnnnnn submitted</t>
-        </is>
-      </c>
-      <c r="G13" s="26" t="inlineStr">
+          <t>New Request and Edit Request (user requests) (SCR-UA-07)</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>Opens a New Request of type Modify user for the new officer, ticks Marketing Team Leader / Head besides the current profile, chooses the approver, writes the justification and clicks Submit</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>The group profiles show the current one and the one added; the request is submitted</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>Pending Approval [Integration scope - UIDM-ISC]</t>
+        </is>
+      </c>
+      <c r="J13" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr"/>
-      <c r="I13" s="12" t="inlineStr"/>
-      <c r="J13" s="12" t="inlineStr"/>
+      <c r="K13" s="12" t="inlineStr"/>
+      <c r="L13" s="12" t="inlineStr"/>
+      <c r="M13" s="12" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -2558,27 +2665,42 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
+          <t>Ulysses Abad</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
           <t>uamapprover</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>Opens the request: the Details tab shows the group profiles added; clicks Approve and Apply</t>
-        </is>
-      </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>The status is Approved; the user receives Your access changed in the app and by e-mail</t>
-        </is>
-      </c>
-      <c r="G14" s="26" t="inlineStr">
+          <t>Access Request record (SCR-UA-08)</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>Opens the request: the Details tab shows the group profile added; clicks Approve and Apply</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>The status is Approved; the user is told Your access changed in the system and by e-mail</t>
+        </is>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>Change applied [Integration scope - UIDM-ISC]</t>
+        </is>
+      </c>
+      <c r="J14" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H14" s="12" t="inlineStr"/>
-      <c r="I14" s="12" t="inlineStr"/>
-      <c r="J14" s="12" t="inlineStr"/>
+      <c r="K14" s="12" t="inlineStr"/>
+      <c r="L14" s="12" t="inlineStr"/>
+      <c r="M14" s="12" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -2593,32 +2715,47 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Second approver</t>
+          <t>Second Approver</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
+          <t>Selina Reyes</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
           <t>secapprover</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>Opens AR-2026-900008 from the Second Approval tab: the tag Privilege increase, first approved by the Approver; clicks Second Approval and confirms</t>
-        </is>
-      </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>The status is Approved; the alert Privileged access change stays in the Alert inbox as evidence</t>
-        </is>
-      </c>
-      <c r="G15" s="26" t="inlineStr">
+          <t>Access Request record (SCR-UA-08)</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>Opens the privileged change from the Second Approval tab: tagged Privilege increase and first approved by the Approver; clicks Second Approval and confirms</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>The status is Approved; the alert Privileged access change is kept as evidence</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>Second approval given [Integration scope - UIDM-ISC]</t>
+        </is>
+      </c>
+      <c r="J15" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H15" s="12" t="inlineStr"/>
-      <c r="I15" s="12" t="inlineStr"/>
-      <c r="J15" s="12" t="inlineStr"/>
+      <c r="K15" s="12" t="inlineStr"/>
+      <c r="L15" s="12" t="inlineStr"/>
+      <c r="M15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -2638,27 +2775,42 @@
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
+          <t>Bea Villanueva</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
           <t>badmin</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>Opens Group Profile Requests › New Group Profile Request, enters the code RENEWAL_ENQUIRY, the name and description, keeps the level Standard, ticks two permissions, adds the approvers Ulysses Access Approver then the New Business Approver, writes the justification and clicks Submit</t>
-        </is>
-      </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>Toast: AR-yyyy-nnnnnn submitted; the Approvers tab lists the two approvers in order</t>
-        </is>
-      </c>
-      <c r="G16" s="26" t="inlineStr">
+          <t>New Group Profile Request and Edit Request (SCR-UA-12)</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>Opens Group Profile Requests › New Group Profile Request, enters the name Renewal enquiry and its description, keeps the level Standard, ticks two permissions, adds the approvers Ulysses Abad then Andres Bautista, writes the justification and clicks Submit</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>The request is submitted; the Approvers tab lists the two approvers in order</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>Pending Approval (first approver)</t>
+        </is>
+      </c>
+      <c r="J16" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H16" s="12" t="inlineStr"/>
-      <c r="I16" s="12" t="inlineStr"/>
-      <c r="J16" s="12" t="inlineStr"/>
+      <c r="K16" s="12" t="inlineStr"/>
+      <c r="L16" s="12" t="inlineStr"/>
+      <c r="M16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -2678,27 +2830,42 @@
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
+          <t>Ulysses Abad</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
           <t>uamapprover</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>Access Request record (SCR-UA-08)</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>Approves the group-profile request</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>The status stays Pending Approval; the request moves to the New Business Approver, who receives the notice</t>
-        </is>
-      </c>
-      <c r="G17" s="26" t="inlineStr">
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>The status stays Pending Approval; the request moves to the second approver, who receives the notice</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>Next approver</t>
+        </is>
+      </c>
+      <c r="J17" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H17" s="12" t="inlineStr"/>
-      <c r="I17" s="12" t="inlineStr"/>
-      <c r="J17" s="12" t="inlineStr"/>
+      <c r="K17" s="12" t="inlineStr"/>
+      <c r="L17" s="12" t="inlineStr"/>
+      <c r="M17" s="12" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -2713,32 +2880,47 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Approver (New Business Approver</t>
+          <t>Second approver of the group profile</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
+          <t>Andres Bautista</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
           <t>approver</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Access Request record (SCR-UA-08)</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>Opens the request from My Approvals and approves it</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>The status is For Implementation; the System Administrators receive Access request AR-yyyy-nnnnnn to implement</t>
-        </is>
-      </c>
-      <c r="G18" s="26" t="inlineStr">
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>The status is For Implementation; the System Administrators receive the notice to implement it</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>For implementation</t>
+        </is>
+      </c>
+      <c r="J18" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H18" s="12" t="inlineStr"/>
-      <c r="I18" s="12" t="inlineStr"/>
-      <c r="J18" s="12" t="inlineStr"/>
+      <c r="K18" s="12" t="inlineStr"/>
+      <c r="L18" s="12" t="inlineStr"/>
+      <c r="M18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -2758,27 +2940,42 @@
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
+          <t>Samuel Cruz</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>Roles &amp; Permissions (SCR-UA-16)</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
         <is>
           <t>Opens Roles &amp; Permissions, finds the request under Approved Requests to Implement, clicks Implement Request and confirms</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>Toast: AR-yyyy-nnnnnn implemented; the profile appears in the matrix with its two permissions</t>
-        </is>
-      </c>
-      <c r="G19" s="26" t="inlineStr">
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>The request is implemented; the profile appears in the matrix with its two permissions</t>
+        </is>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="J19" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H19" s="12" t="inlineStr"/>
-      <c r="I19" s="12" t="inlineStr"/>
-      <c r="J19" s="12" t="inlineStr"/>
+      <c r="K19" s="12" t="inlineStr"/>
+      <c r="L19" s="12" t="inlineStr"/>
+      <c r="M19" s="12" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -2798,27 +2995,42 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
+          <t>Rhea Santiago</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
           <t>requestor</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>Opens a New Request of type Deactivate user for a013000196, chooses the reason Resigned, leaves the effective date blank, chooses the approver and clicks Submit</t>
-        </is>
-      </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>Toast: AR-yyyy-nnnnnn submitted</t>
-        </is>
-      </c>
-      <c r="G20" s="26" t="inlineStr">
+          <t>New Request and Edit Request (user requests) (SCR-UA-07)</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>Opens a New Request of type Deactivate user for the officer, chooses the reason Resigned, leaves the effective date blank, chooses the approver and clicks Submit</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>The request is submitted</t>
+        </is>
+      </c>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>Pending Approval [Integration scope - UIDM-ISC]</t>
+        </is>
+      </c>
+      <c r="J20" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H20" s="12" t="inlineStr"/>
-      <c r="I20" s="12" t="inlineStr"/>
-      <c r="J20" s="12" t="inlineStr"/>
+      <c r="K20" s="12" t="inlineStr"/>
+      <c r="L20" s="12" t="inlineStr"/>
+      <c r="M20" s="12" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -2838,27 +3050,42 @@
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
+          <t>Ulysses Abad</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
           <t>uamapprover</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>Access Request record (SCR-UA-08)</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
         <is>
           <t>Approves the deactivation</t>
         </is>
       </c>
-      <c r="F21" s="12" t="inlineStr">
+      <c r="H21" s="12" t="inlineStr">
         <is>
           <t>The status is Approved; the user is Disabled and every open session of the user has ended</t>
         </is>
       </c>
-      <c r="G21" s="26" t="inlineStr">
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>User deactivated [Integration scope - UIDM-ISC]</t>
+        </is>
+      </c>
+      <c r="J21" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H21" s="12" t="inlineStr"/>
-      <c r="I21" s="12" t="inlineStr"/>
-      <c r="J21" s="12" t="inlineStr"/>
+      <c r="K21" s="12" t="inlineStr"/>
+      <c r="L21" s="12" t="inlineStr"/>
+      <c r="M21" s="12" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -2878,27 +3105,42 @@
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
+          <t>Samuel Cruz</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>Users (SCR-UA-15)</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>Opens Administration › Users with the status Disabled</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>a013000196 is listed Disabled with the profiles it held; Sessions shows the last session ended by the administrator</t>
-        </is>
-      </c>
-      <c r="G22" s="26" t="inlineStr">
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>The officer is listed Disabled with the profiles held; the sessions show the last session ended</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>Evidence of the revocation</t>
+        </is>
+      </c>
+      <c r="J22" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H22" s="12" t="inlineStr"/>
-      <c r="I22" s="12" t="inlineStr"/>
-      <c r="J22" s="12" t="inlineStr"/>
+      <c r="K22" s="12" t="inlineStr"/>
+      <c r="L22" s="12" t="inlineStr"/>
+      <c r="M22" s="12" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -2918,27 +3160,42 @@
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
+          <t>Rhea Santiago</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
           <t>requestor</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>New Request and Edit Request (user requests) (SCR-UA-07)</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
         <is>
           <t>Opens New Request, enters the user ID ab and clicks Submit without a full name, profile, approver or justification</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr">
+      <c r="H23" s="12" t="inlineStr">
         <is>
           <t>Under the fields: Use 3 to 50 letters, digits, dots, dashes or underscores; Enter the full name of the new user; Select at least one role; Select the approver; Enter the justification. Nothing is saved</t>
         </is>
       </c>
-      <c r="G23" s="26" t="inlineStr">
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>Form corrected [Integration scope - UIDM-ISC]</t>
+        </is>
+      </c>
+      <c r="J23" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H23" s="12" t="inlineStr"/>
-      <c r="I23" s="12" t="inlineStr"/>
-      <c r="J23" s="12" t="inlineStr"/>
+      <c r="K23" s="12" t="inlineStr"/>
+      <c r="L23" s="12" t="inlineStr"/>
+      <c r="M23" s="12" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
@@ -2958,27 +3215,42 @@
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
+          <t>Rhea Santiago</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
           <t>requestor</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>New Request and Edit Request (user requests) (SCR-UA-07)</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t>Enters the user ID a01300019X with the other fields complete and clicks Submit</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr">
+      <c r="H24" s="12" t="inlineStr">
         <is>
           <t>Under the user ID: The user ID must be a letter followed by nine digits, for example a013000196</t>
         </is>
       </c>
-      <c r="G24" s="26" t="inlineStr">
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>User ID corrected [Integration scope - UIDM-ISC]</t>
+        </is>
+      </c>
+      <c r="J24" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H24" s="12" t="inlineStr"/>
-      <c r="I24" s="12" t="inlineStr"/>
-      <c r="J24" s="12" t="inlineStr"/>
+      <c r="K24" s="12" t="inlineStr"/>
+      <c r="L24" s="12" t="inlineStr"/>
+      <c r="M24" s="12" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
@@ -2998,27 +3270,42 @@
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
+          <t>Rhea Santiago</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
           <t>requestor</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>Raises a Modify user request for a013000101, which already has a pending request, and clicks Submit</t>
-        </is>
-      </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>A request for user a013000101 is already waiting for approval, with its reference</t>
-        </is>
-      </c>
-      <c r="G25" s="26" t="inlineStr">
+          <t>New Request and Edit Request (user requests) (SCR-UA-07)</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>Raises a Modify user request for a user who already has a pending request, and clicks Submit</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>A request for the user is already waiting for approval, with its reference</t>
+        </is>
+      </c>
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>Wait for the open request [Integration scope - UIDM-ISC]</t>
+        </is>
+      </c>
+      <c r="J25" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H25" s="12" t="inlineStr"/>
-      <c r="I25" s="12" t="inlineStr"/>
-      <c r="J25" s="12" t="inlineStr"/>
+      <c r="K25" s="12" t="inlineStr"/>
+      <c r="L25" s="12" t="inlineStr"/>
+      <c r="M25" s="12" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
@@ -3038,27 +3325,42 @@
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
+          <t>Rhea Santiago</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
           <t>requestor</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
-        <is>
-          <t>Raises a Modify user request for himself (requestor), ticks an additional profile and clicks Submit</t>
-        </is>
-      </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
+          <t>New Request and Edit Request (user requests) (SCR-UA-07)</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>Raises a Modify user request for his or her own user, ticks an additional profile and clicks Submit</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
           <t>You cannot change your own roles</t>
         </is>
       </c>
-      <c r="G26" s="26" t="inlineStr">
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>Another requester raises it [Integration scope - UIDM-ISC]</t>
+        </is>
+      </c>
+      <c r="J26" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H26" s="12" t="inlineStr"/>
-      <c r="I26" s="12" t="inlineStr"/>
-      <c r="J26" s="12" t="inlineStr"/>
+      <c r="K26" s="12" t="inlineStr"/>
+      <c r="L26" s="12" t="inlineStr"/>
+      <c r="M26" s="12" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
@@ -3078,27 +3380,42 @@
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
+          <t>Rhea Santiago</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
           <t>requestor</t>
         </is>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>New Request and Edit Request (user requests) (SCR-UA-07)</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>Enrols a new user with both the User Access Requestor and the User Access Approver profiles and clicks Submit</t>
         </is>
       </c>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>One user may not hold both User Access Requestor and User Access Approver (separation-of-duties rule SOD-900001): the rule authorised by Information Security</t>
-        </is>
-      </c>
-      <c r="G27" s="26" t="inlineStr">
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>One user may not hold both User Access Requestor and User Access Approver (separation-of-duties rule): the rule authorised by Information Security</t>
+        </is>
+      </c>
+      <c r="I27" s="12" t="inlineStr">
+        <is>
+          <t>One of the two profiles removed [Integration scope - UIDM-ISC]</t>
+        </is>
+      </c>
+      <c r="J27" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H27" s="12" t="inlineStr"/>
-      <c r="I27" s="12" t="inlineStr"/>
-      <c r="J27" s="12" t="inlineStr"/>
+      <c r="K27" s="12" t="inlineStr"/>
+      <c r="L27" s="12" t="inlineStr"/>
+      <c r="M27" s="12" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
@@ -3113,32 +3430,47 @@
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>Approver (New Business Approver</t>
+          <t>Another approver</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
+          <t>Andres Bautista</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
           <t>approver</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
-        <is>
-          <t>Opens AR-2026-900002, assigned to Ulysses Access Approver</t>
-        </is>
-      </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>The request shows no decision button for this approver; a decision would be refused: Request AR-2026-900002 is assigned to uamapprover for approval</t>
-        </is>
-      </c>
-      <c r="G28" s="26" t="inlineStr">
+          <t>Access Request record (SCR-UA-08)</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>Opens a request assigned to Ulysses Abad</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>The request shows no decision button for this approver; a decision would be refused: the request is assigned to another approver</t>
+        </is>
+      </c>
+      <c r="I28" s="12" t="inlineStr">
+        <is>
+          <t>Left to the chosen approver [Integration scope - UIDM-ISC]</t>
+        </is>
+      </c>
+      <c r="J28" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H28" s="12" t="inlineStr"/>
-      <c r="I28" s="12" t="inlineStr"/>
-      <c r="J28" s="12" t="inlineStr"/>
+      <c r="K28" s="12" t="inlineStr"/>
+      <c r="L28" s="12" t="inlineStr"/>
+      <c r="M28" s="12" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
@@ -3158,27 +3490,42 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
+          <t>Samuel Cruz</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="E29" s="12" t="inlineStr">
-        <is>
-          <t>Clicks Implement Request on a group-profile request he raised himself</t>
-        </is>
-      </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
+          <t>Roles &amp; Permissions (SCR-UA-16)</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>Clicks Implement Request on a group-profile request he or she raised</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
           <t>A request is implemented by someone other than its requester</t>
         </is>
       </c>
-      <c r="G29" s="26" t="inlineStr">
+      <c r="I29" s="12" t="inlineStr">
+        <is>
+          <t>Another System Administrator implements it</t>
+        </is>
+      </c>
+      <c r="J29" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H29" s="12" t="inlineStr"/>
-      <c r="I29" s="12" t="inlineStr"/>
-      <c r="J29" s="12" t="inlineStr"/>
+      <c r="K29" s="12" t="inlineStr"/>
+      <c r="L29" s="12" t="inlineStr"/>
+      <c r="M29" s="12" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
@@ -3193,32 +3540,47 @@
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>Subject users of the requests (Marketing AO)</t>
+          <t>Business user</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
+          <t>Maria Santos</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
           <t>a013000101</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
-        <is>
-          <t>User a013000101 enters a wrong password three times, then the right one</t>
-        </is>
-      </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
+          <t>Login (SCR-UA-01)</t>
+        </is>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>Maria Santos enters a wrong password three times, then the right one</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
           <t>Invalid user name or password each time, also for the right password: a locked account is refused with the same message as a wrong password; Users shows the lock to the System Administrator</t>
         </is>
       </c>
-      <c r="G30" s="26" t="inlineStr">
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>Account locked</t>
+        </is>
+      </c>
+      <c r="J30" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H30" s="12" t="inlineStr"/>
-      <c r="I30" s="12" t="inlineStr"/>
-      <c r="J30" s="12" t="inlineStr"/>
+      <c r="K30" s="12" t="inlineStr"/>
+      <c r="L30" s="12" t="inlineStr"/>
+      <c r="M30" s="12" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
@@ -3238,27 +3600,42 @@
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
+          <t>Samuel Cruz</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="E31" s="12" t="inlineStr">
-        <is>
-          <t>Opens Users with the status Locked and clicks Unlock on a013000101</t>
-        </is>
-      </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
+          <t>Users (SCR-UA-15)</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>Opens Users with the status Locked and clicks Unlock on Maria Santos</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="inlineStr">
+        <is>
           <t>The user is Active again; the unlock is in the access change log</t>
         </is>
       </c>
-      <c r="G31" s="26" t="inlineStr">
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>Account unlocked</t>
+        </is>
+      </c>
+      <c r="J31" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H31" s="12" t="inlineStr"/>
-      <c r="I31" s="12" t="inlineStr"/>
-      <c r="J31" s="12" t="inlineStr"/>
+      <c r="K31" s="12" t="inlineStr"/>
+      <c r="L31" s="12" t="inlineStr"/>
+      <c r="M31" s="12" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
@@ -3273,32 +3650,47 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Subject users of the requests (Marketing AO)</t>
+          <t>Business user</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>a013000196</t>
+          <t>Maria Santos</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>The deactivated user a013000196 tries to sign in</t>
+          <t>a013000101</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
+          <t>Login (SCR-UA-01)</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>The deactivated officer tries to sign in</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
           <t>Invalid user name or password, the same message as a wrong password; the attempt does not count towards the lock-out</t>
         </is>
       </c>
-      <c r="G32" s="26" t="inlineStr">
+      <c r="I32" s="12" t="inlineStr">
+        <is>
+          <t>Refused</t>
+        </is>
+      </c>
+      <c r="J32" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H32" s="12" t="inlineStr"/>
-      <c r="I32" s="12" t="inlineStr"/>
-      <c r="J32" s="12" t="inlineStr"/>
+      <c r="K32" s="12" t="inlineStr"/>
+      <c r="L32" s="12" t="inlineStr"/>
+      <c r="M32" s="12" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
@@ -3318,27 +3710,42 @@
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
+          <t>Rhea Santiago</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
           <t>requestor</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>My Profile (SCR-UA-05)</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
         <is>
           <t>On My Profile, types a new password that is too short and has no symbol</t>
         </is>
       </c>
-      <c r="F33" s="12" t="inlineStr">
+      <c r="H33" s="12" t="inlineStr">
         <is>
           <t>Still needed: At least 10 characters; A symbol; Change Password stays disabled</t>
         </is>
       </c>
-      <c r="G33" s="26" t="inlineStr">
+      <c r="I33" s="12" t="inlineStr">
+        <is>
+          <t>Password rules shown</t>
+        </is>
+      </c>
+      <c r="J33" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H33" s="12" t="inlineStr"/>
-      <c r="I33" s="12" t="inlineStr"/>
-      <c r="J33" s="12" t="inlineStr"/>
+      <c r="K33" s="12" t="inlineStr"/>
+      <c r="L33" s="12" t="inlineStr"/>
+      <c r="M33" s="12" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
@@ -3358,32 +3765,47 @@
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
+          <t>Rhea Santiago</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
           <t>requestor</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>My Profile (SCR-UA-05)</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
         <is>
           <t>Enters the current password as the new password and clicks Change Password</t>
         </is>
       </c>
-      <c r="F34" s="12" t="inlineStr">
+      <c r="H34" s="12" t="inlineStr">
         <is>
           <t>You used this password recently. Choose another one</t>
         </is>
       </c>
-      <c r="G34" s="26" t="inlineStr">
+      <c r="I34" s="12" t="inlineStr">
+        <is>
+          <t>Another password chosen</t>
+        </is>
+      </c>
+      <c r="J34" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H34" s="12" t="inlineStr"/>
-      <c r="I34" s="12" t="inlineStr"/>
-      <c r="J34" s="12" t="inlineStr"/>
+      <c r="K34" s="12" t="inlineStr"/>
+      <c r="L34" s="12" t="inlineStr"/>
+      <c r="M34" s="12" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>WT-D The evidence of access</t>
+          <t>WT-D The evidence of access for the Auditor and Information Security</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
@@ -3398,32 +3820,47 @@
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
+          <t>Audrey Lim</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
           <t>auditor</t>
         </is>
       </c>
-      <c r="E35" s="12" t="inlineStr">
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>User Access Matrix (SCR-UA-13)</t>
+        </is>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
         <is>
           <t>Opens User Access › User Access Matrix, By Action, and searches USER ACCESS</t>
         </is>
       </c>
-      <c r="F35" s="12" t="inlineStr">
+      <c r="H35" s="12" t="inlineStr">
         <is>
           <t>The User Access area by action class, with the permissions each profile holds: the Requestor creates and amends, the Approver approves, the Second Approver gives the second approval</t>
         </is>
       </c>
-      <c r="G35" s="26" t="inlineStr">
+      <c r="I35" s="12" t="inlineStr">
+        <is>
+          <t>Matrix reviewed</t>
+        </is>
+      </c>
+      <c r="J35" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H35" s="12" t="inlineStr"/>
-      <c r="I35" s="12" t="inlineStr"/>
-      <c r="J35" s="12" t="inlineStr"/>
+      <c r="K35" s="12" t="inlineStr"/>
+      <c r="L35" s="12" t="inlineStr"/>
+      <c r="M35" s="12" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>WT-D The evidence of access</t>
+          <t>WT-D The evidence of access for the Auditor and Information Security</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
@@ -3438,32 +3875,47 @@
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
+          <t>Audrey Lim</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
           <t>auditor</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr">
-        <is>
-          <t>Runs the User Group Profile Report for the profile UAM_APPROVER</t>
-        </is>
-      </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>The modules and tasks of the Approver with With Access, and the dates and actors of its creation and last change</t>
-        </is>
-      </c>
-      <c r="G36" s="26" t="inlineStr">
+          <t>User access report (report runner) (SCR-UA-17)</t>
+        </is>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>Runs the User Group Profile Report for the profile User Access Approver</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>The modules and tasks of the profile with With Access, and the dates and actors of its creation and last change</t>
+        </is>
+      </c>
+      <c r="I36" s="12" t="inlineStr">
+        <is>
+          <t>Profile content reviewed</t>
+        </is>
+      </c>
+      <c r="J36" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H36" s="12" t="inlineStr"/>
-      <c r="I36" s="12" t="inlineStr"/>
-      <c r="J36" s="12" t="inlineStr"/>
+      <c r="K36" s="12" t="inlineStr"/>
+      <c r="L36" s="12" t="inlineStr"/>
+      <c r="M36" s="12" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>WT-D The evidence of access</t>
+          <t>WT-D The evidence of access for the Auditor and Information Security</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
@@ -3478,34 +3930,159 @@
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
+          <t>Audrey Lim</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
           <t>auditor</t>
         </is>
       </c>
-      <c r="E37" s="12" t="inlineStr">
-        <is>
-          <t>Runs Group Profile Membership for MKT_AO as of today</t>
-        </is>
-      </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
+          <t>User access report (report runner) (SCR-UA-17)</t>
+        </is>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>Runs Group Profile Membership for Marketing Account Officer as of today</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="inlineStr">
+        <is>
           <t>The members of the Marketing Account Officer profile with who added each and when</t>
         </is>
       </c>
-      <c r="G37" s="26" t="inlineStr">
+      <c r="I37" s="12" t="inlineStr">
+        <is>
+          <t>Members reviewed</t>
+        </is>
+      </c>
+      <c r="J37" s="26" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="H37" s="12" t="inlineStr"/>
-      <c r="I37" s="12" t="inlineStr"/>
-      <c r="J37" s="12" t="inlineStr"/>
+      <c r="K37" s="12" t="inlineStr"/>
+      <c r="L37" s="12" t="inlineStr"/>
+      <c r="M37" s="12" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>WT-D The evidence of access for the Auditor and Information Security</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>WT-D.4</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>Auditor</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>Audrey Lim</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>auditor</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>User access report (report runner) (SCR-UA-17)</t>
+        </is>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>Runs the User Access Audit Log for today with the activity Group Profile Changes</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>The creation of the group profile Renewal enquiry with its permissions, the request number, Done By and Approved By, with the from and to values</t>
+        </is>
+      </c>
+      <c r="I38" s="12" t="inlineStr">
+        <is>
+          <t>Group-profile changes reviewed</t>
+        </is>
+      </c>
+      <c r="J38" s="26" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="K38" s="12" t="inlineStr"/>
+      <c r="L38" s="12" t="inlineStr"/>
+      <c r="M38" s="12" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>WT-D The evidence of access for the Auditor and Information Security</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>WT-D.5</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>Auditor</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>Audrey Lim</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>auditor</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>User access report (report runner) (SCR-UA-17)</t>
+        </is>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>Runs the User Access Report as of today for every status</t>
+        </is>
+      </c>
+      <c r="H39" s="12" t="inlineStr">
+        <is>
+          <t>Every user with the group profiles held, the status, who created and last changed the access and when, under the report header</t>
+        </is>
+      </c>
+      <c r="I39" s="12" t="inlineStr">
+        <is>
+          <t>Access as of a date reviewed</t>
+        </is>
+      </c>
+      <c r="J39" s="26" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="K39" s="12" t="inlineStr"/>
+      <c r="L39" s="12" t="inlineStr"/>
+      <c r="M39" s="12" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J37"/>
+  <autoFilter ref="A4:M39"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:M2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G5:G537">
+  <conditionalFormatting sqref="J5:J539">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"Pass"</formula>
     </cfRule>
@@ -3516,13 +4093,13 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:J537">
+  <conditionalFormatting sqref="A5:M539">
     <cfRule type="expression" priority="4" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G5:G537" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Result" error="Choose a value from the list (Result)." type="list">
+    <dataValidation sqref="J5:J539" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Result" error="Choose a value from the list (Result)." type="list">
       <formula1>'Lists'!$A$2:$A$5</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_UAT_BRD-11_Business_Unit_Walkthrough_Users_v1.1.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_UAT_BRD-11_Business_Unit_Walkthrough_Users_v1.1.xlsx
@@ -952,7 +952,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -1379,7 +1379,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -2022,7 +2022,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -4107,7 +4107,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -4169,7 +4169,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_UAT_BRD-11_Business_Unit_Walkthrough_Users_v1.1.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_UAT_BRD-11_Business_Unit_Walkthrough_Users_v1.1.xlsx
@@ -2020,7 +2020,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
@@ -4105,7 +4105,7 @@
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Walkthrough Users&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
